--- a/diseases/d014/2015-2019.xlsx
+++ b/diseases/d014/2015-2019.xlsx
@@ -769,11 +769,11 @@
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0001432527072226987</v>
+        <v>0.0001445859780518485</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1509,11 +1509,11 @@
         <v>1</v>
       </c>
       <c r="R7" t="n">
-        <v>7.162635361134937e-05</v>
+        <v>7.229298902592427e-05</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -2249,11 +2249,11 @@
         <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>0.0002148790608340481</v>
+        <v>0.0002168789670777728</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -2989,11 +2989,11 @@
         <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>7.162635361134937e-05</v>
+        <v>7.229298902592427e-05</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -3733,7 +3733,7 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
@@ -5357,11 +5357,11 @@
         <v>1</v>
       </c>
       <c r="R33" t="n">
-        <v>7.162635361134937e-05</v>
+        <v>7.229298902592427e-05</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
@@ -6249,7 +6249,7 @@
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
@@ -6989,7 +6989,7 @@
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
@@ -7729,7 +7729,7 @@
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
@@ -8617,7 +8617,7 @@
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
@@ -9357,7 +9357,7 @@
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
@@ -10093,11 +10093,11 @@
         <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>7.122240129813025e-05</v>
+        <v>7.182256952424729e-05</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
@@ -10985,7 +10985,7 @@
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
@@ -11725,7 +11725,7 @@
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
@@ -12465,7 +12465,7 @@
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
@@ -13349,11 +13349,11 @@
         <v>1</v>
       </c>
       <c r="R87" t="n">
-        <v>7.122240129813025e-05</v>
+        <v>7.182256952424729e-05</v>
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO87" t="inlineStr">
@@ -14093,7 +14093,7 @@
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO92" t="inlineStr">
@@ -14833,7 +14833,7 @@
       </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO97" t="inlineStr">
@@ -15721,7 +15721,7 @@
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO103" t="inlineStr">
@@ -16461,7 +16461,7 @@
       </c>
       <c r="S108" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO108" t="inlineStr">
@@ -17349,7 +17349,7 @@
       </c>
       <c r="S114" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO114" t="inlineStr">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="S119" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO119" t="inlineStr">
@@ -18829,7 +18829,7 @@
       </c>
       <c r="S124" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO124" t="inlineStr">
@@ -19717,7 +19717,7 @@
       </c>
       <c r="S130" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO130" t="inlineStr">
@@ -20457,7 +20457,7 @@
       </c>
       <c r="S135" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO135" t="inlineStr">
@@ -21197,7 +21197,7 @@
       </c>
       <c r="S140" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO140" t="inlineStr">
@@ -22085,7 +22085,7 @@
       </c>
       <c r="S146" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO146" t="inlineStr">
@@ -22825,7 +22825,7 @@
       </c>
       <c r="S151" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO151" t="inlineStr">
@@ -23565,7 +23565,7 @@
       </c>
       <c r="S156" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO156" t="inlineStr">
@@ -24453,7 +24453,7 @@
       </c>
       <c r="S162" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO162" t="inlineStr">
@@ -25193,7 +25193,7 @@
       </c>
       <c r="S167" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO167" t="inlineStr">
@@ -25933,7 +25933,7 @@
       </c>
       <c r="S172" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO172" t="inlineStr">
@@ -26821,7 +26821,7 @@
       </c>
       <c r="S178" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO178" t="inlineStr">
@@ -27561,7 +27561,7 @@
       </c>
       <c r="S183" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO183" t="inlineStr">
@@ -28301,7 +28301,7 @@
       </c>
       <c r="S188" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO188" t="inlineStr">
@@ -29189,7 +29189,7 @@
       </c>
       <c r="S194" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO194" t="inlineStr">
@@ -29929,7 +29929,7 @@
       </c>
       <c r="S199" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO199" t="inlineStr">
@@ -30669,7 +30669,7 @@
       </c>
       <c r="S204" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO204" t="inlineStr">
@@ -31557,7 +31557,7 @@
       </c>
       <c r="S210" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO210" t="inlineStr">
@@ -32297,7 +32297,7 @@
       </c>
       <c r="S215" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO215" t="inlineStr">
@@ -33037,7 +33037,7 @@
       </c>
       <c r="S220" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO220" t="inlineStr">
@@ -33925,7 +33925,7 @@
       </c>
       <c r="S226" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO226" t="inlineStr">
@@ -34665,7 +34665,7 @@
       </c>
       <c r="S231" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO231" t="inlineStr">
@@ -35553,7 +35553,7 @@
       </c>
       <c r="S237" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO237" t="inlineStr">
@@ -36293,7 +36293,7 @@
       </c>
       <c r="S242" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO242" t="inlineStr">
@@ -37033,7 +37033,7 @@
       </c>
       <c r="S247" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO247" t="inlineStr">
@@ -37921,7 +37921,7 @@
       </c>
       <c r="S253" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO253" t="inlineStr">
@@ -38661,7 +38661,7 @@
       </c>
       <c r="S258" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO258" t="inlineStr">
@@ -39401,7 +39401,7 @@
       </c>
       <c r="S263" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO263" t="inlineStr">
@@ -40141,7 +40141,7 @@
       </c>
       <c r="S268" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO268" t="inlineStr">
@@ -41029,7 +41029,7 @@
       </c>
       <c r="S274" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO274" t="inlineStr">
@@ -41769,7 +41769,7 @@
       </c>
       <c r="S279" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO279" t="inlineStr">
@@ -42657,7 +42657,7 @@
       </c>
       <c r="S285" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO285" t="inlineStr">
@@ -43397,7 +43397,7 @@
       </c>
       <c r="S290" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO290" t="inlineStr">
@@ -44137,7 +44137,7 @@
       </c>
       <c r="S295" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO295" t="inlineStr">
@@ -45025,7 +45025,7 @@
       </c>
       <c r="S301" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO301" t="inlineStr">
@@ -45765,7 +45765,7 @@
       </c>
       <c r="S306" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO306" t="inlineStr">
@@ -46505,7 +46505,7 @@
       </c>
       <c r="S311" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO311" t="inlineStr">
@@ -47393,7 +47393,7 @@
       </c>
       <c r="S317" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO317" t="inlineStr">

--- a/diseases/d014/2015-2019.xlsx
+++ b/diseases/d014/2015-2019.xlsx
@@ -776,6 +776,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1516,6 +1521,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2256,6 +2266,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2996,6 +3011,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3736,6 +3756,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4624,6 +4649,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5364,6 +5394,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6252,6 +6287,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6992,6 +7032,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7732,6 +7777,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8620,6 +8670,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO55" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9360,6 +9415,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10100,6 +10160,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO65" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10988,6 +11053,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO71" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11728,6 +11798,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO76" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12468,6 +12543,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO81" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13356,6 +13436,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO87" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14096,6 +14181,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO92" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14836,6 +14926,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO97" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15724,6 +15819,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO103" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16464,6 +16564,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO108" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17352,6 +17457,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO114" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18092,6 +18202,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO119" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18832,6 +18947,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO124" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19720,6 +19840,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO130" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20460,6 +20585,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO135" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21200,6 +21330,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO140" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22088,6 +22223,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO146" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22828,6 +22968,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO151" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23568,6 +23713,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO156" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24456,6 +24606,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO162" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25196,6 +25351,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO167" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25936,6 +26096,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO172" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26824,6 +26989,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA178" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO178" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27564,6 +27734,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA183" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO183" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28304,6 +28479,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA188" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO188" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29192,6 +29372,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA194" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO194" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29932,6 +30117,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA199" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO199" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30672,6 +30862,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO204" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31560,6 +31755,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA210" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO210" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32300,6 +32500,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA215" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO215" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33040,6 +33245,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA220" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO220" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33928,6 +34138,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA226" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO226" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34668,6 +34883,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA231" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO231" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35556,6 +35776,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA237" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO237" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36296,6 +36521,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA242" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO242" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37036,6 +37266,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA247" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO247" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37924,6 +38159,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA253" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO253" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38664,6 +38904,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA258" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO258" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39404,6 +39649,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA263" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO263" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40144,6 +40394,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA268" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO268" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41032,6 +41287,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA274" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO274" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41772,6 +42032,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA279" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO279" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42660,6 +42925,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA285" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO285" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43400,6 +43670,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA290" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO290" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44140,6 +44415,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA295" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO295" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45028,6 +45308,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA301" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO301" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45768,6 +46053,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA306" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO306" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46508,6 +46798,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA311" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO311" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -47394,6 +47689,11 @@
       <c r="S317" t="inlineStr">
         <is>
           <t>nbs_computed</t>
+        </is>
+      </c>
+      <c r="AA317" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO317" t="inlineStr">
